--- a/ENGL317/Project4 - Usability Testing/RawData.xlsx
+++ b/ENGL317/Project4 - Usability Testing/RawData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects Stuff\GitHub Repos\Classwork\ENGL317\Project4 - Usability Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509A5E9D-8412-4C46-88AF-6EDFAC9DE059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA9ED10F-416E-42D8-8691-8A4C1FA22A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{493A8161-AC38-4C26-94CC-A6AF262AC730}"/>
+    <workbookView xWindow="28680" yWindow="1290" windowWidth="21840" windowHeight="13740" xr2:uid="{493A8161-AC38-4C26-94CC-A6AF262AC730}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="27">
   <si>
     <t>Efficient</t>
   </si>
@@ -87,6 +87,36 @@
   </si>
   <si>
     <t>Task Three</t>
+  </si>
+  <si>
+    <t>Task 1</t>
+  </si>
+  <si>
+    <t>Task 2</t>
+  </si>
+  <si>
+    <t>Task 3</t>
+  </si>
+  <si>
+    <t>Task 4</t>
+  </si>
+  <si>
+    <t>Task 5</t>
+  </si>
+  <si>
+    <t>Task 6</t>
+  </si>
+  <si>
+    <t>Task 7</t>
+  </si>
+  <si>
+    <t>Task 8</t>
+  </si>
+  <si>
+    <t>Task 9</t>
+  </si>
+  <si>
+    <t>Task 10</t>
   </si>
 </sst>
 </file>
@@ -1205,7 +1235,7 @@
                   <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>46</c:v>
@@ -1339,7 +1369,7 @@
                   <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>37</c:v>
@@ -1473,6 +1503,533 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="622414640"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Score</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Per Task</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Bluesky</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$59:$K$59</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Task 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Task 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Task 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Task 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Task 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Task 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Task 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Task 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Task 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Task 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$60:$K$60</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5B64-499F-8A3E-C33FCF8A67F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$61</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>X (Twitter)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$59:$K$59</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Task 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Task 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Task 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Task 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Task 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Task 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Task 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Task 8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Task 9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Task 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$61:$K$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5B64-499F-8A3E-C33FCF8A67F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="475165416"/>
+        <c:axId val="475164336"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="475165416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="475164336"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="475164336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="475165416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2138,7 +2695,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>6</c:v>
@@ -2215,7 +2772,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2</c:v>
@@ -5129,6 +5686,46 @@
 </file>
 
 <file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6496,6 +7093,509 @@
 
 <file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -11385,16 +12485,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>80962</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>285750</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11414,6 +12514,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="13" name="Chart 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0E51522-B54A-608F-1D97-B292F7DC12F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11739,10 +12875,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E97D327-33AD-4241-846C-5B9236E1D273}">
-  <dimension ref="A2:G56"/>
+  <dimension ref="A2:K61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -11762,7 +12898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -11781,720 +12917,762 @@
       <c r="F3">
         <v>6</v>
       </c>
-      <c r="G3">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>6</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24">
+        <v>5</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>5</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33">
+        <v>6</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>6</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43">
+        <v>4</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43">
+        <v>6</v>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44">
+        <v>6</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44">
+        <v>3</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>6</v>
+      </c>
+      <c r="D48">
+        <v>6</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49">
+        <v>5</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2</v>
+      </c>
+      <c r="E54" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55">
+        <f t="shared" ref="B55:F56" si="0">SUM(B3,B8,B13,B18,B23,B28,B33,B38,B43,B48)</f>
+        <v>52</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="G55">
+        <f>SUM(B55:F55)</f>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="G56">
+        <f>SUM(B56:F56)</f>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" t="s">
+        <v>20</v>
+      </c>
+      <c r="F59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" t="s">
+        <v>24</v>
+      </c>
+      <c r="J59" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60">
         <f>SUM(B3:F3)</f>
         <v>27</v>
       </c>
+      <c r="C60">
+        <f>SUM(B8:F8)</f>
+        <v>30</v>
+      </c>
+      <c r="D60">
+        <f>SUM(B13:F13)</f>
+        <v>24</v>
+      </c>
+      <c r="E60">
+        <f>SUM(B18:F18)</f>
+        <v>23</v>
+      </c>
+      <c r="F60">
+        <f>SUM(B23:F23)</f>
+        <v>21</v>
+      </c>
+      <c r="G60">
+        <f>SUM(B28:F28)</f>
+        <v>20</v>
+      </c>
+      <c r="H60">
+        <f>SUM(B33:F33)</f>
+        <v>26</v>
+      </c>
+      <c r="I60">
+        <f>SUM(B38:F38)</f>
+        <v>25</v>
+      </c>
+      <c r="J60">
+        <f>SUM(B43:F43)</f>
+        <v>25</v>
+      </c>
+      <c r="K60">
+        <f>SUM(B48:F48)</f>
+        <v>27</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
+      <c r="B61">
         <f>SUM(B4:F4)</f>
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
-        <v>6</v>
-      </c>
-      <c r="G8">
-        <f>SUM(B8:F8)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>6</v>
-      </c>
-      <c r="F9">
-        <v>6</v>
-      </c>
-      <c r="G9">
+      <c r="C61">
         <f>SUM(B9:F9)</f>
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="F13">
-        <v>6</v>
-      </c>
-      <c r="G13">
-        <f>SUM(B13:F13)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14">
-        <v>6</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14">
+      <c r="D61">
         <f>SUM(B14:F14)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18">
-        <v>6</v>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <v>6</v>
-      </c>
-      <c r="G18">
-        <f>SUM(B18:F18)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>6</v>
-      </c>
-      <c r="E19">
-        <v>5</v>
-      </c>
-      <c r="F19">
-        <v>5</v>
-      </c>
-      <c r="G19">
+        <v>21</v>
+      </c>
+      <c r="E61">
         <f>SUM(B19:F19)</f>
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23">
-        <v>5</v>
-      </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23">
-        <v>6</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23">
-        <v>4</v>
-      </c>
-      <c r="G23">
-        <f>SUM(B23:F23)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <v>5</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>5</v>
-      </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24">
+      <c r="F61">
         <f>SUM(B24:F24)</f>
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" t="s">
-        <v>3</v>
-      </c>
-      <c r="F27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
-      </c>
-      <c r="C28">
-        <v>5</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28">
-        <v>5</v>
-      </c>
-      <c r="F28">
-        <v>4</v>
-      </c>
-      <c r="G28">
-        <f>SUM(B28:F28)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29">
-        <v>6</v>
-      </c>
-      <c r="C29">
-        <v>5</v>
-      </c>
-      <c r="D29">
-        <v>5</v>
-      </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29">
-        <v>5</v>
-      </c>
-      <c r="G29">
+      <c r="G61">
         <f>SUM(B29:F29)</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1</v>
-      </c>
-      <c r="D32" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33">
-        <v>6</v>
-      </c>
-      <c r="C33">
-        <v>6</v>
-      </c>
-      <c r="D33">
-        <v>6</v>
-      </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
-      <c r="F33">
-        <v>6</v>
-      </c>
-      <c r="G33">
-        <f>SUM(B33:F33)</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34">
+      <c r="H61">
         <f>SUM(B34:F34)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" t="s">
-        <v>3</v>
-      </c>
-      <c r="F37" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38">
-        <v>6</v>
-      </c>
-      <c r="C38">
-        <v>6</v>
-      </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="E38">
-        <v>5</v>
-      </c>
-      <c r="F38">
-        <v>6</v>
-      </c>
-      <c r="G38">
-        <f>SUM(B38:F38)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39">
-        <v>2</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-      <c r="D39">
-        <v>6</v>
-      </c>
-      <c r="E39">
-        <v>3</v>
-      </c>
-      <c r="F39">
-        <v>5</v>
-      </c>
-      <c r="G39">
+      <c r="I61">
         <f>SUM(B39:F39)</f>
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" t="s">
-        <v>2</v>
-      </c>
-      <c r="E42" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43">
-        <v>3</v>
-      </c>
-      <c r="C43">
-        <v>4</v>
-      </c>
-      <c r="D43">
-        <v>6</v>
-      </c>
-      <c r="E43">
-        <v>6</v>
-      </c>
-      <c r="F43">
-        <v>6</v>
-      </c>
-      <c r="G43">
-        <f>SUM(B43:F43)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44">
-        <v>5</v>
-      </c>
-      <c r="C44">
-        <v>6</v>
-      </c>
-      <c r="D44">
-        <v>2</v>
-      </c>
-      <c r="E44">
-        <v>3</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44">
+      <c r="J61">
         <f>SUM(B44:F44)</f>
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" t="s">
-        <v>2</v>
-      </c>
-      <c r="E47" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>5</v>
-      </c>
-      <c r="B48">
-        <v>6</v>
-      </c>
-      <c r="C48">
-        <v>6</v>
-      </c>
-      <c r="D48">
-        <v>6</v>
-      </c>
-      <c r="E48">
-        <v>3</v>
-      </c>
-      <c r="F48">
-        <v>6</v>
-      </c>
-      <c r="G48">
-        <f>SUM(B48:F48)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49">
-        <v>5</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>5</v>
-      </c>
-      <c r="E49">
-        <v>6</v>
-      </c>
-      <c r="F49">
-        <v>4</v>
-      </c>
-      <c r="G49">
+      <c r="K61">
         <f>SUM(B49:F49)</f>
         <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1</v>
-      </c>
-      <c r="D54" t="s">
-        <v>2</v>
-      </c>
-      <c r="E54" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>5</v>
-      </c>
-      <c r="B55">
-        <f>SUM(B3,B8,B13,B18,B23,B28,B33,B38,B43,B48)</f>
-        <v>52</v>
-      </c>
-      <c r="C55">
-        <f>SUM(C3,C8,C13,C18,C23,C28,C33,C38,C43,C48)</f>
-        <v>49</v>
-      </c>
-      <c r="D55">
-        <f>SUM(D3,D8,D13,D18,D23,D28,D33,D38,D43,D48)</f>
-        <v>46</v>
-      </c>
-      <c r="E55">
-        <f>SUM(E3,E8,E13,E18,E23,E28,E33,E38,E43,E48)</f>
-        <v>46</v>
-      </c>
-      <c r="F55">
-        <f>SUM(F3,F8,F13,F18,F23,F28,F33,F38,F43,F48)</f>
-        <v>56</v>
-      </c>
-      <c r="G55">
-        <f>SUM(B55:F55)</f>
-        <v>249</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56">
-        <f>SUM(B4,B9,B14,B19,B24,B29,B34,B39,B44,B49)</f>
-        <v>38</v>
-      </c>
-      <c r="C56">
-        <f>SUM(C4,C9,C14,C19,C24,C29,C34,C39,C44,C49)</f>
-        <v>40</v>
-      </c>
-      <c r="D56">
-        <f>SUM(D4,D9,D14,D19,D24,D29,D34,D39,D44,D49)</f>
-        <v>38</v>
-      </c>
-      <c r="E56">
-        <f>SUM(E4,E9,E14,E19,E24,E29,E34,E39,E44,E49)</f>
-        <v>37</v>
-      </c>
-      <c r="F56">
-        <f>SUM(F4,F9,F14,F19,F24,F29,F34,F39,F44,F49)</f>
-        <v>37</v>
-      </c>
-      <c r="G56">
-        <f>SUM(B56:F56)</f>
-        <v>190</v>
       </c>
     </row>
   </sheetData>
